--- a/Result/profitability/4147.xlsx
+++ b/Result/profitability/4147.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM60"/>
+  <dimension ref="A1:AM61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
         <v>-1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.29875</v>
+        <v>-0.315</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
@@ -766,7 +766,7 @@
         <v>-0.99</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.405</v>
+        <v>-0.3825000000000001</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -873,7 +873,7 @@
         <v>-0.71</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4375</v>
+        <v>-0.46</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -980,7 +980,7 @@
         <v>-0.7</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5137499999999999</v>
+        <v>-0.52</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -7790,6 +7790,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>4147</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>156</v>
+      </c>
+      <c r="D61" t="n">
+        <v>77</v>
+      </c>
+      <c r="E61" t="n">
+        <v>79</v>
+      </c>
+      <c r="F61" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-75</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-47.91%</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>2</v>
+      </c>
+      <c r="J61" t="n">
+        <v>-73</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-73</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-0.17625</v>
+      </c>
+      <c r="N61" t="n">
+        <v>42.8625</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W61" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="X61" t="n">
+        <v>-5.500000000000001</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-0.1888</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>-0.05000000000000002</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0.2272727272727273</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.660000000000004</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.03384991843393159</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK61" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
